--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -235,10 +235,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -253,14 +253,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -279,10 +271,25 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -294,26 +301,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -324,16 +315,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -354,8 +338,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -370,15 +378,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -386,17 +387,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -409,25 +409,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,13 +427,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,13 +451,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,19 +469,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -517,7 +541,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -529,67 +571,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -612,15 +612,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -632,17 +623,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,6 +642,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -673,15 +662,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -700,6 +680,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -708,145 +708,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2488,7 +2488,7 @@
         <v>20</v>
       </c>
       <c r="D76">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>49</v>
@@ -2573,7 +2573,7 @@
         <v>20</v>
       </c>
       <c r="D81">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>49</v>
@@ -2743,7 +2743,7 @@
         <v>20</v>
       </c>
       <c r="D91">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>49</v>
@@ -3015,7 +3015,7 @@
         <v>30</v>
       </c>
       <c r="D107">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>49</v>
@@ -3032,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="D108">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>49</v>
@@ -3270,7 +3270,7 @@
         <v>30</v>
       </c>
       <c r="D122">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>49</v>
@@ -3287,7 +3287,7 @@
         <v>20</v>
       </c>
       <c r="D123">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>49</v>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="71">
   <si>
     <t>Id</t>
   </si>
@@ -235,10 +235,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -257,14 +257,38 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,7 +304,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,8 +324,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,40 +348,24 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -363,22 +386,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -386,17 +393,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -409,13 +409,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,7 +439,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,7 +535,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -457,127 +577,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,7 +589,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,8 +605,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -627,16 +629,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -666,32 +677,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -700,6 +685,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -708,145 +708,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1176,7 +1176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="19.2727272727273" customWidth="1"/>
@@ -2567,13 +2567,13 @@
         <v>50030</v>
       </c>
       <c r="B81">
-        <v>4010</v>
+        <v>1020</v>
       </c>
       <c r="C81">
-        <v>20</v>
+        <v>6020</v>
       </c>
       <c r="D81">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>49</v>
@@ -2587,7 +2587,7 @@
         <v>1020</v>
       </c>
       <c r="C82">
-        <v>6020</v>
+        <v>6030</v>
       </c>
       <c r="D82">
         <v>50</v>
@@ -2604,7 +2604,7 @@
         <v>1020</v>
       </c>
       <c r="C83">
-        <v>6030</v>
+        <v>6040</v>
       </c>
       <c r="D83">
         <v>50</v>
@@ -2621,7 +2621,7 @@
         <v>1020</v>
       </c>
       <c r="C84">
-        <v>6040</v>
+        <v>6050</v>
       </c>
       <c r="D84">
         <v>50</v>
@@ -2638,7 +2638,7 @@
         <v>1020</v>
       </c>
       <c r="C85">
-        <v>6050</v>
+        <v>6060</v>
       </c>
       <c r="D85">
         <v>50</v>
@@ -2652,13 +2652,13 @@
         <v>50030</v>
       </c>
       <c r="B86">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C86">
-        <v>6060</v>
+        <v>1010</v>
       </c>
       <c r="D86">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>49</v>
@@ -2666,16 +2666,16 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B87">
         <v>1010</v>
       </c>
       <c r="C87">
-        <v>4010</v>
+        <v>1020</v>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>49</v>
@@ -2683,16 +2683,16 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B88">
         <v>1010</v>
       </c>
       <c r="C88">
-        <v>4020</v>
+        <v>1030</v>
       </c>
       <c r="D88">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>49</v>
@@ -2700,16 +2700,16 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B89">
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>5050</v>
+        <v>1040</v>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>49</v>
@@ -2717,16 +2717,16 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B90">
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>5060</v>
+        <v>1050</v>
       </c>
       <c r="D90">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>49</v>
@@ -2734,7 +2734,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B91">
         <v>4010</v>
@@ -2757,10 +2757,10 @@
         <v>1010</v>
       </c>
       <c r="C92">
-        <v>4310</v>
+        <v>4010</v>
       </c>
       <c r="D92">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>49</v>
@@ -2774,10 +2774,10 @@
         <v>1010</v>
       </c>
       <c r="C93">
-        <v>1010</v>
+        <v>4020</v>
       </c>
       <c r="D93">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>49</v>
@@ -2791,10 +2791,10 @@
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>1020</v>
+        <v>4030</v>
       </c>
       <c r="D94">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>49</v>
@@ -2808,10 +2808,10 @@
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>1030</v>
+        <v>5050</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>49</v>
@@ -2825,10 +2825,10 @@
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>1040</v>
+        <v>5060</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>49</v>
@@ -2842,10 +2842,10 @@
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>1050</v>
+        <v>4310</v>
       </c>
       <c r="D97">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>49</v>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B98">
         <v>1010</v>
@@ -2862,7 +2862,7 @@
         <v>1110</v>
       </c>
       <c r="D98">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>49</v>
@@ -2870,7 +2870,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B99">
         <v>1010</v>
@@ -2879,7 +2879,7 @@
         <v>1120</v>
       </c>
       <c r="D99">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>49</v>
@@ -2887,7 +2887,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B100">
         <v>1010</v>
@@ -2896,7 +2896,7 @@
         <v>1130</v>
       </c>
       <c r="D100">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>49</v>
@@ -2904,7 +2904,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B101">
         <v>1010</v>
@@ -2913,7 +2913,7 @@
         <v>1140</v>
       </c>
       <c r="D101">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>49</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B102">
         <v>1010</v>
@@ -2930,7 +2930,7 @@
         <v>1150</v>
       </c>
       <c r="D102">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>49</v>
@@ -2938,16 +2938,16 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B103">
         <v>1010</v>
       </c>
       <c r="C103">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="D103">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>49</v>
@@ -2955,16 +2955,16 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B104">
         <v>1010</v>
       </c>
       <c r="C104">
-        <v>4020</v>
+        <v>1020</v>
       </c>
       <c r="D104">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>49</v>
@@ -2972,16 +2972,16 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B105">
         <v>1010</v>
       </c>
       <c r="C105">
-        <v>4020</v>
+        <v>1030</v>
       </c>
       <c r="D105">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>49</v>
@@ -2989,16 +2989,16 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B106">
         <v>1010</v>
       </c>
       <c r="C106">
-        <v>4030</v>
+        <v>1040</v>
       </c>
       <c r="D106">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>49</v>
@@ -3006,16 +3006,16 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B107">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C107">
-        <v>30</v>
+        <v>1050</v>
       </c>
       <c r="D107">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>49</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B108">
         <v>4010</v>
@@ -3046,10 +3046,10 @@
         <v>1010</v>
       </c>
       <c r="C109">
-        <v>4310</v>
+        <v>1110</v>
       </c>
       <c r="D109">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>49</v>
@@ -3063,10 +3063,10 @@
         <v>1010</v>
       </c>
       <c r="C110">
-        <v>5010</v>
+        <v>1120</v>
       </c>
       <c r="D110">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>49</v>
@@ -3080,10 +3080,10 @@
         <v>1010</v>
       </c>
       <c r="C111">
-        <v>5020</v>
+        <v>1130</v>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>49</v>
@@ -3091,13 +3091,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B112">
         <v>1010</v>
       </c>
       <c r="C112">
-        <v>1110</v>
+        <v>1140</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -3108,13 +3108,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B113">
         <v>1010</v>
       </c>
       <c r="C113">
-        <v>1120</v>
+        <v>1150</v>
       </c>
       <c r="D113">
         <v>15</v>
@@ -3125,16 +3125,16 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B114">
         <v>1010</v>
       </c>
       <c r="C114">
-        <v>1130</v>
+        <v>4010</v>
       </c>
       <c r="D114">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>49</v>
@@ -3142,16 +3142,16 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B115">
         <v>1010</v>
       </c>
       <c r="C115">
-        <v>1140</v>
+        <v>4020</v>
       </c>
       <c r="D115">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>49</v>
@@ -3159,16 +3159,16 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B116">
         <v>1010</v>
       </c>
       <c r="C116">
-        <v>1150</v>
+        <v>4020</v>
       </c>
       <c r="D116">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>49</v>
@@ -3176,16 +3176,16 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B117">
         <v>1010</v>
       </c>
       <c r="C117">
-        <v>4010</v>
+        <v>4030</v>
       </c>
       <c r="D117">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>49</v>
@@ -3193,16 +3193,16 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B118">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C118">
-        <v>4020</v>
+        <v>30</v>
       </c>
       <c r="D118">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>49</v>
@@ -3210,16 +3210,16 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B119">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C119">
-        <v>4020</v>
+        <v>20</v>
       </c>
       <c r="D119">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>49</v>
@@ -3227,16 +3227,16 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B120">
         <v>1010</v>
       </c>
       <c r="C120">
-        <v>4030</v>
+        <v>4310</v>
       </c>
       <c r="D120">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>49</v>
@@ -3244,16 +3244,16 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B121">
         <v>1010</v>
       </c>
       <c r="C121">
-        <v>4030</v>
+        <v>5010</v>
       </c>
       <c r="D121">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>49</v>
@@ -3261,16 +3261,16 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B122">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C122">
-        <v>30</v>
+        <v>5020</v>
       </c>
       <c r="D122">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>49</v>
@@ -3281,13 +3281,13 @@
         <v>50060</v>
       </c>
       <c r="B123">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C123">
-        <v>20</v>
+        <v>1110</v>
       </c>
       <c r="D123">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>49</v>
@@ -3301,10 +3301,10 @@
         <v>1010</v>
       </c>
       <c r="C124">
-        <v>4310</v>
+        <v>1120</v>
       </c>
       <c r="D124">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>49</v>
@@ -3318,10 +3318,10 @@
         <v>1010</v>
       </c>
       <c r="C125">
-        <v>5010</v>
+        <v>1130</v>
       </c>
       <c r="D125">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>49</v>
@@ -3335,10 +3335,10 @@
         <v>1010</v>
       </c>
       <c r="C126">
-        <v>5020</v>
+        <v>1140</v>
       </c>
       <c r="D126">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>49</v>
@@ -3346,35 +3346,222 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127">
-        <v>60010</v>
+        <v>50060</v>
       </c>
       <c r="B127">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C127">
-        <v>50</v>
+        <v>1150</v>
       </c>
       <c r="D127">
-        <v>1</v>
-      </c>
-      <c r="E127" t="s">
-        <v>50</v>
+        <v>15</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128">
+        <v>50060</v>
+      </c>
+      <c r="B128">
+        <v>1010</v>
+      </c>
+      <c r="C128">
+        <v>4010</v>
+      </c>
+      <c r="D128">
+        <v>4</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129">
+        <v>50060</v>
+      </c>
+      <c r="B129">
+        <v>1010</v>
+      </c>
+      <c r="C129">
+        <v>4020</v>
+      </c>
+      <c r="D129">
+        <v>8</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130">
+        <v>50060</v>
+      </c>
+      <c r="B130">
+        <v>1010</v>
+      </c>
+      <c r="C130">
+        <v>4020</v>
+      </c>
+      <c r="D130">
+        <v>8</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131">
+        <v>50060</v>
+      </c>
+      <c r="B131">
+        <v>1010</v>
+      </c>
+      <c r="C131">
+        <v>4030</v>
+      </c>
+      <c r="D131">
+        <v>12</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132">
+        <v>50060</v>
+      </c>
+      <c r="B132">
+        <v>1010</v>
+      </c>
+      <c r="C132">
+        <v>4030</v>
+      </c>
+      <c r="D132">
+        <v>12</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133">
+        <v>50060</v>
+      </c>
+      <c r="B133">
+        <v>4010</v>
+      </c>
+      <c r="C133">
+        <v>30</v>
+      </c>
+      <c r="D133">
+        <v>100</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134">
+        <v>50060</v>
+      </c>
+      <c r="B134">
+        <v>4010</v>
+      </c>
+      <c r="C134">
+        <v>20</v>
+      </c>
+      <c r="D134">
+        <v>100</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135">
+        <v>50060</v>
+      </c>
+      <c r="B135">
+        <v>1010</v>
+      </c>
+      <c r="C135">
+        <v>4310</v>
+      </c>
+      <c r="D135">
+        <v>30</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136">
+        <v>50060</v>
+      </c>
+      <c r="B136">
+        <v>1010</v>
+      </c>
+      <c r="C136">
+        <v>5010</v>
+      </c>
+      <c r="D136">
+        <v>5</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137">
+        <v>50060</v>
+      </c>
+      <c r="B137">
+        <v>1010</v>
+      </c>
+      <c r="C137">
+        <v>5020</v>
+      </c>
+      <c r="D137">
+        <v>5</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138">
         <v>60010</v>
       </c>
-      <c r="B128">
+      <c r="B138">
+        <v>2020</v>
+      </c>
+      <c r="C138">
+        <v>50</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139">
+        <v>60010</v>
+      </c>
+      <c r="B139">
         <v>2</v>
       </c>
-      <c r="C128">
+      <c r="C139">
         <v>20</v>
       </c>
-      <c r="D128">
+      <c r="D139">
         <v>0</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E139" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -235,9 +235,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -257,83 +257,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -348,7 +272,75 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -356,14 +348,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -386,6 +370,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -393,10 +393,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -409,7 +409,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -421,31 +445,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -457,37 +535,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,61 +565,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,25 +589,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -600,17 +600,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -639,16 +628,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,17 +651,28 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -708,145 +708,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3556,13 +3556,13 @@
         <v>2</v>
       </c>
       <c r="C139">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -149,7 +149,19 @@
     <t>ポーション</t>
   </si>
   <si>
+    <t>ポーションx2</t>
+  </si>
+  <si>
+    <t>ポーションx3</t>
+  </si>
+  <si>
     <t>ハイポーション</t>
+  </si>
+  <si>
+    <t>ハイポーションx2</t>
+  </si>
+  <si>
+    <t>ハイポーションx3</t>
   </si>
   <si>
     <t>Rankアップ</t>
@@ -235,10 +247,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -257,37 +269,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,9 +282,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,7 +306,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,22 +314,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -361,8 +342,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -370,17 +352,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -399,6 +373,44 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -409,55 +421,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,19 +439,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -499,7 +463,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -511,67 +571,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,7 +589,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -603,6 +615,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -618,11 +641,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,41 +667,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -700,6 +694,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -708,145 +720,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1176,7 +1188,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="19.2727272727273" customWidth="1"/>
@@ -2219,7 +2231,7 @@
         <v>2</v>
       </c>
       <c r="E60" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2236,7 +2248,7 @@
         <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2253,143 +2265,143 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>20010</v>
+        <v>15062</v>
       </c>
       <c r="B63">
-        <v>2010</v>
+        <v>1010</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>5060</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>31010</v>
+        <v>15063</v>
       </c>
       <c r="B64">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C64">
-        <v>1010</v>
+        <v>5060</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>31020</v>
+        <v>20010</v>
       </c>
       <c r="B65">
-        <v>1020</v>
+        <v>2010</v>
       </c>
       <c r="C65">
-        <v>1020</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>40010</v>
+        <v>31010</v>
       </c>
       <c r="B66">
-        <v>2020</v>
+        <v>1020</v>
       </c>
       <c r="C66">
-        <v>15</v>
+        <v>1010</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>40020</v>
+        <v>31020</v>
       </c>
       <c r="B67">
-        <v>2020</v>
+        <v>1020</v>
       </c>
       <c r="C67">
-        <v>10</v>
+        <v>1020</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>40030</v>
+        <v>40010</v>
       </c>
       <c r="B68">
         <v>2020</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>50010</v>
+        <v>40020</v>
       </c>
       <c r="B69">
-        <v>1020</v>
+        <v>2020</v>
       </c>
       <c r="C69">
-        <v>6010</v>
+        <v>10</v>
       </c>
       <c r="D69">
-        <v>25</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="E69" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>50010</v>
+        <v>40030</v>
       </c>
       <c r="B70">
-        <v>1010</v>
+        <v>2020</v>
       </c>
       <c r="C70">
-        <v>4010</v>
+        <v>5</v>
       </c>
       <c r="D70">
-        <v>4</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2397,50 +2409,50 @@
         <v>50010</v>
       </c>
       <c r="B71">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C71">
-        <v>5050</v>
+        <v>6010</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B72">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C72">
-        <v>6010</v>
+        <v>4010</v>
       </c>
       <c r="D72">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>50020</v>
+        <v>50010</v>
       </c>
       <c r="B73">
         <v>1010</v>
       </c>
       <c r="C73">
-        <v>4010</v>
+        <v>5050</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2448,16 +2460,16 @@
         <v>50020</v>
       </c>
       <c r="B74">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C74">
-        <v>4020</v>
+        <v>6010</v>
       </c>
       <c r="D74">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2468,13 +2480,13 @@
         <v>1010</v>
       </c>
       <c r="C75">
-        <v>5050</v>
+        <v>4010</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2482,50 +2494,50 @@
         <v>50020</v>
       </c>
       <c r="B76">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C76">
-        <v>20</v>
+        <v>4020</v>
       </c>
       <c r="D76">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B77">
         <v>1010</v>
       </c>
       <c r="C77">
-        <v>4010</v>
+        <v>5050</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>50030</v>
+        <v>50020</v>
       </c>
       <c r="B78">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C78">
-        <v>4020</v>
+        <v>20</v>
       </c>
       <c r="D78">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2536,13 +2548,13 @@
         <v>1010</v>
       </c>
       <c r="C79">
-        <v>5050</v>
+        <v>4010</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2553,13 +2565,13 @@
         <v>1010</v>
       </c>
       <c r="C80">
-        <v>5060</v>
+        <v>4020</v>
       </c>
       <c r="D80">
         <v>8</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2567,16 +2579,16 @@
         <v>50030</v>
       </c>
       <c r="B81">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C81">
-        <v>6020</v>
+        <v>5050</v>
       </c>
       <c r="D81">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2584,16 +2596,16 @@
         <v>50030</v>
       </c>
       <c r="B82">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C82">
-        <v>6030</v>
+        <v>5060</v>
       </c>
       <c r="D82">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2604,13 +2616,13 @@
         <v>1020</v>
       </c>
       <c r="C83">
-        <v>6040</v>
+        <v>6020</v>
       </c>
       <c r="D83">
         <v>50</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2621,13 +2633,13 @@
         <v>1020</v>
       </c>
       <c r="C84">
-        <v>6050</v>
+        <v>6030</v>
       </c>
       <c r="D84">
         <v>50</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2638,13 +2650,13 @@
         <v>1020</v>
       </c>
       <c r="C85">
-        <v>6060</v>
+        <v>6040</v>
       </c>
       <c r="D85">
         <v>50</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2652,16 +2664,16 @@
         <v>50030</v>
       </c>
       <c r="B86">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C86">
-        <v>1010</v>
+        <v>6050</v>
       </c>
       <c r="D86">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2669,16 +2681,16 @@
         <v>50030</v>
       </c>
       <c r="B87">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C87">
-        <v>1020</v>
+        <v>6060</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2689,13 +2701,13 @@
         <v>1010</v>
       </c>
       <c r="C88">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="D88">
         <v>10</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2706,13 +2718,13 @@
         <v>1010</v>
       </c>
       <c r="C89">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="D89">
         <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2723,13 +2735,13 @@
         <v>1010</v>
       </c>
       <c r="C90">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="D90">
         <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2737,50 +2749,50 @@
         <v>50030</v>
       </c>
       <c r="B91">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C91">
-        <v>20</v>
+        <v>1040</v>
       </c>
       <c r="D91">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B92">
         <v>1010</v>
       </c>
       <c r="C92">
-        <v>4010</v>
+        <v>1050</v>
       </c>
       <c r="D92">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>50040</v>
+        <v>50030</v>
       </c>
       <c r="B93">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C93">
-        <v>4020</v>
+        <v>20</v>
       </c>
       <c r="D93">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2791,13 +2803,13 @@
         <v>1010</v>
       </c>
       <c r="C94">
-        <v>4030</v>
+        <v>4010</v>
       </c>
       <c r="D94">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2808,13 +2820,13 @@
         <v>1010</v>
       </c>
       <c r="C95">
-        <v>5050</v>
+        <v>4020</v>
       </c>
       <c r="D95">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2825,13 +2837,13 @@
         <v>1010</v>
       </c>
       <c r="C96">
-        <v>5060</v>
+        <v>4030</v>
       </c>
       <c r="D96">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2842,13 +2854,13 @@
         <v>1010</v>
       </c>
       <c r="C97">
-        <v>4310</v>
+        <v>5050</v>
       </c>
       <c r="D97">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2859,13 +2871,13 @@
         <v>1010</v>
       </c>
       <c r="C98">
-        <v>1110</v>
+        <v>5060</v>
       </c>
       <c r="D98">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2876,13 +2888,13 @@
         <v>1010</v>
       </c>
       <c r="C99">
-        <v>1120</v>
+        <v>4310</v>
       </c>
       <c r="D99">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2893,13 +2905,13 @@
         <v>1010</v>
       </c>
       <c r="C100">
-        <v>1130</v>
+        <v>1110</v>
       </c>
       <c r="D100">
         <v>10</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2910,13 +2922,13 @@
         <v>1010</v>
       </c>
       <c r="C101">
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="D101">
         <v>10</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2927,13 +2939,13 @@
         <v>1010</v>
       </c>
       <c r="C102">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="D102">
         <v>10</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2944,13 +2956,13 @@
         <v>1010</v>
       </c>
       <c r="C103">
-        <v>1010</v>
+        <v>1140</v>
       </c>
       <c r="D103">
         <v>10</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2961,13 +2973,13 @@
         <v>1010</v>
       </c>
       <c r="C104">
-        <v>1020</v>
+        <v>1150</v>
       </c>
       <c r="D104">
         <v>10</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2978,13 +2990,13 @@
         <v>1010</v>
       </c>
       <c r="C105">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="D105">
         <v>10</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2995,13 +3007,13 @@
         <v>1010</v>
       </c>
       <c r="C106">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="D106">
         <v>10</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3012,13 +3024,13 @@
         <v>1010</v>
       </c>
       <c r="C107">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="D107">
         <v>10</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3026,50 +3038,50 @@
         <v>50040</v>
       </c>
       <c r="B108">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C108">
-        <v>20</v>
+        <v>1040</v>
       </c>
       <c r="D108">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B109">
         <v>1010</v>
       </c>
       <c r="C109">
-        <v>1110</v>
+        <v>1050</v>
       </c>
       <c r="D109">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>50050</v>
+        <v>50040</v>
       </c>
       <c r="B110">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C110">
-        <v>1120</v>
+        <v>20</v>
       </c>
       <c r="D110">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3080,13 +3092,13 @@
         <v>1010</v>
       </c>
       <c r="C111">
-        <v>1130</v>
+        <v>1110</v>
       </c>
       <c r="D111">
         <v>15</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3097,13 +3109,13 @@
         <v>1010</v>
       </c>
       <c r="C112">
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="D112">
         <v>15</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3114,13 +3126,13 @@
         <v>1010</v>
       </c>
       <c r="C113">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="D113">
         <v>15</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3131,13 +3143,13 @@
         <v>1010</v>
       </c>
       <c r="C114">
-        <v>4010</v>
+        <v>1140</v>
       </c>
       <c r="D114">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3148,13 +3160,13 @@
         <v>1010</v>
       </c>
       <c r="C115">
-        <v>4020</v>
+        <v>1150</v>
       </c>
       <c r="D115">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3165,13 +3177,13 @@
         <v>1010</v>
       </c>
       <c r="C116">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D116">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3182,13 +3194,13 @@
         <v>1010</v>
       </c>
       <c r="C117">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D117">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3196,16 +3208,16 @@
         <v>50050</v>
       </c>
       <c r="B118">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C118">
-        <v>30</v>
+        <v>4020</v>
       </c>
       <c r="D118">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3213,16 +3225,16 @@
         <v>50050</v>
       </c>
       <c r="B119">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C119">
-        <v>20</v>
+        <v>4030</v>
       </c>
       <c r="D119">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3230,16 +3242,16 @@
         <v>50050</v>
       </c>
       <c r="B120">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C120">
-        <v>4310</v>
+        <v>30</v>
       </c>
       <c r="D120">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3247,16 +3259,16 @@
         <v>50050</v>
       </c>
       <c r="B121">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C121">
-        <v>5010</v>
+        <v>20</v>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3267,47 +3279,47 @@
         <v>1010</v>
       </c>
       <c r="C122">
-        <v>5020</v>
+        <v>4310</v>
       </c>
       <c r="D122">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B123">
         <v>1010</v>
       </c>
       <c r="C123">
-        <v>1110</v>
+        <v>5010</v>
       </c>
       <c r="D123">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124">
-        <v>50060</v>
+        <v>50050</v>
       </c>
       <c r="B124">
         <v>1010</v>
       </c>
       <c r="C124">
-        <v>1120</v>
+        <v>5020</v>
       </c>
       <c r="D124">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3318,13 +3330,13 @@
         <v>1010</v>
       </c>
       <c r="C125">
-        <v>1130</v>
+        <v>1110</v>
       </c>
       <c r="D125">
         <v>15</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3335,13 +3347,13 @@
         <v>1010</v>
       </c>
       <c r="C126">
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="D126">
         <v>15</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3352,13 +3364,13 @@
         <v>1010</v>
       </c>
       <c r="C127">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="D127">
         <v>15</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3369,13 +3381,13 @@
         <v>1010</v>
       </c>
       <c r="C128">
-        <v>4010</v>
+        <v>1140</v>
       </c>
       <c r="D128">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3386,13 +3398,13 @@
         <v>1010</v>
       </c>
       <c r="C129">
-        <v>4020</v>
+        <v>1150</v>
       </c>
       <c r="D129">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3403,13 +3415,13 @@
         <v>1010</v>
       </c>
       <c r="C130">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D130">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3420,13 +3432,13 @@
         <v>1010</v>
       </c>
       <c r="C131">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D131">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3437,13 +3449,13 @@
         <v>1010</v>
       </c>
       <c r="C132">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="D132">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3451,16 +3463,16 @@
         <v>50060</v>
       </c>
       <c r="B133">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C133">
-        <v>30</v>
+        <v>4030</v>
       </c>
       <c r="D133">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3468,16 +3480,16 @@
         <v>50060</v>
       </c>
       <c r="B134">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="C134">
-        <v>20</v>
+        <v>4030</v>
       </c>
       <c r="D134">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3485,16 +3497,16 @@
         <v>50060</v>
       </c>
       <c r="B135">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C135">
-        <v>4310</v>
+        <v>30</v>
       </c>
       <c r="D135">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3502,16 +3514,16 @@
         <v>50060</v>
       </c>
       <c r="B136">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="C136">
-        <v>5010</v>
+        <v>20</v>
       </c>
       <c r="D136">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3522,46 +3534,80 @@
         <v>1010</v>
       </c>
       <c r="C137">
-        <v>5020</v>
+        <v>4310</v>
       </c>
       <c r="D137">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138">
-        <v>60010</v>
+        <v>50060</v>
       </c>
       <c r="B138">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="C138">
-        <v>50</v>
+        <v>5010</v>
       </c>
       <c r="D138">
-        <v>1</v>
-      </c>
-      <c r="E138" t="s">
-        <v>50</v>
+        <v>5</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139">
+        <v>50060</v>
+      </c>
+      <c r="B139">
+        <v>1010</v>
+      </c>
+      <c r="C139">
+        <v>5020</v>
+      </c>
+      <c r="D139">
+        <v>5</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140">
         <v>60010</v>
       </c>
-      <c r="B139">
+      <c r="B140">
+        <v>2020</v>
+      </c>
+      <c r="C140">
+        <v>50</v>
+      </c>
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="E140" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141">
+        <v>60010</v>
+      </c>
+      <c r="B141">
         <v>2</v>
       </c>
-      <c r="C139">
+      <c r="C141">
         <v>25</v>
       </c>
-      <c r="D139">
+      <c r="D141">
         <v>0</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E141" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3580,7 +3626,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3588,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3596,7 +3642,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3604,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3612,7 +3658,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3628,7 +3674,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3636,7 +3682,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3644,7 +3690,7 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3652,7 +3698,7 @@
         <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3660,7 +3706,7 @@
         <v>100</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3668,7 +3714,7 @@
         <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3676,7 +3722,7 @@
         <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3684,7 +3730,7 @@
         <v>1010</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3692,7 +3738,7 @@
         <v>1020</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3700,7 +3746,7 @@
         <v>2010</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3708,7 +3754,7 @@
         <v>2020</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3716,7 +3762,7 @@
         <v>2030</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3724,7 +3770,7 @@
         <v>2040</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3732,7 +3778,7 @@
         <v>4010</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3740,7 +3786,7 @@
         <v>4020</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/PrizeSets.xlsx
+++ b/Assets/Data/PrizeSets.xlsx
@@ -249,8 +249,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -268,6 +268,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -282,6 +312,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,77 +327,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -375,7 +344,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -390,6 +382,22 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -397,16 +405,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -421,13 +421,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,7 +505,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,25 +517,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -481,31 +565,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -517,25 +577,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,55 +595,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -612,17 +612,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -637,21 +626,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -673,9 +647,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -708,7 +684,31 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -720,145 +720,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
